--- a/data/gravel/Haute Sauce 2025.xlsx
+++ b/data/gravel/Haute Sauce 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DC5D680-3338-C04F-A62F-1C699B0F5044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D903DF26-6700-EE45-AB96-FC7384AAF720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="31000" yWindow="-20960" windowWidth="25940" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -266,9 +266,6 @@
     <t>threaded</t>
   </si>
   <si>
-    <t>a8:g38</t>
-  </si>
-  <si>
     <t>usd</t>
   </si>
   <si>
@@ -477,6 +474,9 @@
   </si>
   <si>
     <t>XS/S</t>
+  </si>
+  <si>
+    <t>a8:k36</t>
   </si>
 </sst>
 </file>
@@ -846,7 +846,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -854,7 +854,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -878,36 +878,36 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C6" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="I6" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="K6" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -915,34 +915,34 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>77</v>
+        <v>147</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="I7" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="K7" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
@@ -950,34 +950,34 @@
         <v>6</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="I8" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="J8" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="J8" s="1" t="s">
+      <c r="K8" s="1" t="s">
         <v>145</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -985,7 +985,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" s="1">
         <v>500</v>
@@ -1020,7 +1020,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C10" s="1">
         <v>385</v>
@@ -1055,7 +1055,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C11" s="1">
         <v>69</v>
@@ -1090,7 +1090,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C12" s="1">
         <v>74.5</v>
@@ -1125,7 +1125,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C13" s="1">
         <v>90</v>
@@ -1160,7 +1160,7 @@
         <v>17</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C14" s="1">
         <v>358</v>
@@ -1195,7 +1195,7 @@
         <v>16</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C15" s="1">
         <v>505</v>
@@ -1230,7 +1230,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C16" s="1">
         <v>694</v>
@@ -1265,7 +1265,7 @@
         <v>19</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C17" s="1">
         <v>160</v>
@@ -1300,7 +1300,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C18" s="1">
         <v>60</v>
@@ -1332,10 +1332,10 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C19" s="1">
         <v>284</v>
@@ -1370,7 +1370,7 @@
         <v>12</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C20" s="1">
         <f>VALUE(LEFT(L20,3))</f>
@@ -1409,31 +1409,31 @@
         <v>426</v>
       </c>
       <c r="L20" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="N20" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="M20" s="1" t="s">
+      <c r="O20" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="N20" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="O20" s="1" t="s">
-        <v>109</v>
-      </c>
       <c r="P20" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S20" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.3">
@@ -1441,7 +1441,7 @@
         <v>22</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C21" s="1">
         <v>395</v>
@@ -1476,7 +1476,7 @@
         <v>18</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C22" s="1">
         <v>45</v>
@@ -1511,7 +1511,7 @@
         <v>73</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C23" s="1">
         <v>84</v>
@@ -1546,7 +1546,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C24" s="1">
         <f>VALUE(LEFT(L24,3))</f>
@@ -1585,39 +1585,39 @@
         <v>1105</v>
       </c>
       <c r="L24" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="M24" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="M24" s="1" t="s">
+      <c r="N24" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="N24" s="1" t="s">
+      <c r="O24" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="O24" s="1" t="s">
+      <c r="P24" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="P24" s="1" t="s">
+      <c r="Q24" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="Q24" s="1" t="s">
+      <c r="R24" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="R24" s="1" t="s">
+      <c r="S24" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="S24" s="1" t="s">
+      <c r="T24" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="T24" s="1" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C25" s="1">
         <f>VALUE(LEFT(L25,3))</f>
@@ -1656,31 +1656,31 @@
         <v>700</v>
       </c>
       <c r="L25" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="M25" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="M25" s="1" t="s">
+      <c r="N25" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="N25" s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="O25" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="S25" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.3">
@@ -1691,10 +1691,10 @@
         <v>70</v>
       </c>
       <c r="L26" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="M26" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="M26" s="1" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.3">
@@ -1880,7 +1880,7 @@
         <v>31</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
@@ -2016,7 +2016,7 @@
         <v>51</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
@@ -2024,7 +2024,7 @@
         <v>52</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
@@ -2119,7 +2119,7 @@
         <v>65</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Haute Sauce 2025.xlsx
+++ b/data/gravel/Haute Sauce 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D903DF26-6700-EE45-AB96-FC7384AAF720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6331E2A9-0320-2249-A590-C2FC18B86DC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31000" yWindow="-20960" windowWidth="25940" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8560" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="149">
   <si>
     <t>brand</t>
   </si>
@@ -477,6 +477,9 @@
   </si>
   <si>
     <t>a8:k36</t>
+  </si>
+  <si>
+    <t>https://haute.bike/cdn/shop/files/SIDEmade-bike-show-2023-haute-swood_10-2000x1334.jpg?v=1694551759&amp;width=1070</t>
   </si>
 </sst>
 </file>
@@ -882,6 +885,9 @@
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>148</v>
+      </c>
       <c r="C6" s="3" t="s">
         <v>78</v>
       </c>

--- a/data/gravel/Haute Sauce 2025.xlsx
+++ b/data/gravel/Haute Sauce 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6331E2A9-0320-2249-A590-C2FC18B86DC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CDD2826-AA6E-D540-9984-D8E5D20D07BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8560" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10280" yWindow="780" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="151">
   <si>
     <t>brand</t>
   </si>
@@ -266,9 +266,6 @@
     <t>threaded</t>
   </si>
   <si>
-    <t>usd</t>
-  </si>
-  <si>
     <t>Size 0</t>
   </si>
   <si>
@@ -480,6 +477,15 @@
   </si>
   <si>
     <t>https://haute.bike/cdn/shop/files/SIDEmade-bike-show-2023-haute-swood_10-2000x1334.jpg?v=1694551759&amp;width=1070</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Richmond, Virginia, USA</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -837,7 +843,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T76"/>
+  <dimension ref="A1:T77"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -849,7 +855,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -857,7 +863,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -881,39 +887,39 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="I6" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="K6" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -921,34 +927,34 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="I7" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="K7" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
@@ -956,34 +962,34 @@
         <v>6</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="I8" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="J8" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="J8" s="1" t="s">
+      <c r="K8" s="1" t="s">
         <v>144</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -991,7 +997,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C9" s="1">
         <v>500</v>
@@ -1026,7 +1032,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C10" s="1">
         <v>385</v>
@@ -1061,7 +1067,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C11" s="1">
         <v>69</v>
@@ -1096,7 +1102,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C12" s="1">
         <v>74.5</v>
@@ -1131,7 +1137,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C13" s="1">
         <v>90</v>
@@ -1166,7 +1172,7 @@
         <v>17</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C14" s="1">
         <v>358</v>
@@ -1201,7 +1207,7 @@
         <v>16</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C15" s="1">
         <v>505</v>
@@ -1236,7 +1242,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C16" s="1">
         <v>694</v>
@@ -1271,7 +1277,7 @@
         <v>19</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C17" s="1">
         <v>160</v>
@@ -1306,7 +1312,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C18" s="1">
         <v>60</v>
@@ -1338,10 +1344,10 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C19" s="1">
         <v>284</v>
@@ -1376,7 +1382,7 @@
         <v>12</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C20" s="1">
         <f>VALUE(LEFT(L20,3))</f>
@@ -1415,31 +1421,31 @@
         <v>426</v>
       </c>
       <c r="L20" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="N20" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="M20" s="1" t="s">
+      <c r="O20" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="N20" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="O20" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="P20" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="S20" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.3">
@@ -1447,7 +1453,7 @@
         <v>22</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C21" s="1">
         <v>395</v>
@@ -1482,7 +1488,7 @@
         <v>18</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C22" s="1">
         <v>45</v>
@@ -1517,7 +1523,7 @@
         <v>73</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C23" s="1">
         <v>84</v>
@@ -1552,7 +1558,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C24" s="1">
         <f>VALUE(LEFT(L24,3))</f>
@@ -1591,39 +1597,39 @@
         <v>1105</v>
       </c>
       <c r="L24" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="M24" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="M24" s="1" t="s">
+      <c r="N24" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="N24" s="1" t="s">
+      <c r="O24" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="O24" s="1" t="s">
+      <c r="P24" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="P24" s="1" t="s">
+      <c r="Q24" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="Q24" s="1" t="s">
+      <c r="R24" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="R24" s="1" t="s">
+      <c r="S24" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="S24" s="1" t="s">
+      <c r="T24" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="T24" s="1" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C25" s="1">
         <f>VALUE(LEFT(L25,3))</f>
@@ -1662,31 +1668,31 @@
         <v>700</v>
       </c>
       <c r="L25" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="M25" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="M25" s="1" t="s">
+      <c r="N25" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="N25" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="O25" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S25" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.3">
@@ -1697,10 +1703,10 @@
         <v>70</v>
       </c>
       <c r="L26" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="M26" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="M26" s="1" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.3">
@@ -1886,7 +1892,7 @@
         <v>31</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
@@ -2022,7 +2028,7 @@
         <v>51</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
@@ -2030,7 +2036,7 @@
         <v>52</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
@@ -2125,7 +2131,15 @@
         <v>65</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>77</v>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>149</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Haute Sauce 2025.xlsx
+++ b/data/gravel/Haute Sauce 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CDD2826-AA6E-D540-9984-D8E5D20D07BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01BD15E2-178A-9344-99A9-64CFCD2CCFAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10280" yWindow="780" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="157">
   <si>
     <t>brand</t>
   </si>
@@ -486,6 +486,24 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -843,7 +861,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T77"/>
+  <dimension ref="A1:T83"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1965,180 +1983,210 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>76</v>
+        <v>151</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>43</v>
+        <v>152</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B55" s="1">
-        <v>27.2</v>
+        <v>153</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>72</v>
+        <v>154</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B57" s="1">
-        <v>44</v>
+        <v>155</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>47</v>
+        <v>156</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B60" s="1">
-        <v>180</v>
+        <v>43</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B61" s="1">
+        <v>27.2</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>138</v>
+        <v>72</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>137</v>
+        <v>46</v>
+      </c>
+      <c r="B63" s="1">
+        <v>44</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B66" s="1">
-        <v>2</v>
+        <v>180</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B67" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>72</v>
+        <v>138</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>72</v>
+        <v>137</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>72</v>
+        <v>55</v>
+      </c>
+      <c r="B72" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B73" s="1">
-        <v>1799</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B74" s="1">
-        <v>3599</v>
+        <v>57</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>150</v>
+        <v>72</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B79" s="1">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B80" s="1">
+        <v>3599</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="B83" s="1" t="s">
         <v>149</v>
       </c>
     </row>

--- a/data/gravel/Haute Sauce 2025.xlsx
+++ b/data/gravel/Haute Sauce 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01BD15E2-178A-9344-99A9-64CFCD2CCFAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46031F02-6B15-334F-82F5-F7C0CC7159CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -470,9 +470,6 @@
     <t>XXL</t>
   </si>
   <si>
-    <t>XS/S</t>
-  </si>
-  <si>
     <t>a8:k36</t>
   </si>
   <si>
@@ -504,6 +501,9 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>XXS</t>
   </si>
 </sst>
 </file>
@@ -910,7 +910,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>77</v>
@@ -945,7 +945,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>86</v>
@@ -983,10 +983,10 @@
         <v>129</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>145</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>140</v>
@@ -1983,32 +1983,32 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
@@ -2179,15 +2179,15 @@
         <v>65</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>149</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Haute Sauce 2025.xlsx
+++ b/data/gravel/Haute Sauce 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46031F02-6B15-334F-82F5-F7C0CC7159CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{167AC2B8-76AC-6540-A21D-0498B6CEFEE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34800" yWindow="-24580" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="159">
   <si>
     <t>brand</t>
   </si>
@@ -434,9 +434,6 @@
     <t>tire_size</t>
   </si>
   <si>
-    <t>titanium</t>
-  </si>
-  <si>
     <t>https://haute.bike/pages/get-lost-in-the-sauce</t>
   </si>
   <si>
@@ -504,6 +501,15 @@
   </si>
   <si>
     <t>XXS</t>
+  </si>
+  <si>
+    <t>steel</t>
+  </si>
+  <si>
+    <t>ZS44/28.6</t>
+  </si>
+  <si>
+    <t>EC44/40</t>
   </si>
 </sst>
 </file>
@@ -873,7 +879,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -881,7 +887,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -905,12 +911,12 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>77</v>
@@ -945,7 +951,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>86</v>
@@ -983,31 +989,31 @@
         <v>129</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>112</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>110</v>
       </c>
       <c r="J8" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -1910,7 +1916,7 @@
         <v>31</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
@@ -1983,32 +1989,41 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
+      </c>
+      <c r="B53" s="1">
+        <v>44</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
@@ -2076,7 +2091,7 @@
         <v>51</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
@@ -2084,7 +2099,7 @@
         <v>52</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
@@ -2179,15 +2194,15 @@
         <v>65</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>147</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Haute Sauce 2025.xlsx
+++ b/data/gravel/Haute Sauce 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{167AC2B8-76AC-6540-A21D-0498B6CEFEE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{316E3680-EE97-7648-ACA0-F3B9FB30333A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34800" yWindow="-24580" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32440" yWindow="-24580" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="157">
   <si>
     <t>brand</t>
   </si>
@@ -257,12 +257,6 @@
     <t>trail</t>
   </si>
   <si>
-    <t>rider_min_spec</t>
-  </si>
-  <si>
-    <t>rider_max_spec</t>
-  </si>
-  <si>
     <t>threaded</t>
   </si>
   <si>
@@ -467,9 +461,6 @@
     <t>XXL</t>
   </si>
   <si>
-    <t>a8:k36</t>
-  </si>
-  <si>
     <t>https://haute.bike/cdn/shop/files/SIDEmade-bike-show-2023-haute-swood_10-2000x1334.jpg?v=1694551759&amp;width=1070</t>
   </si>
   <si>
@@ -510,6 +501,9 @@
   </si>
   <si>
     <t>EC44/40</t>
+  </si>
+  <si>
+    <t>a8:k34</t>
   </si>
 </sst>
 </file>
@@ -867,7 +861,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T83"/>
+  <dimension ref="A1:T81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -879,7 +873,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -887,7 +881,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -911,39 +905,39 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="H6" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="I6" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="K6" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -951,34 +945,34 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="G7" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="H7" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="I7" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="K7" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
@@ -986,34 +980,34 @@
         <v>6</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="F8" s="1" t="s">
+      <c r="I8" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>141</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -1021,7 +1015,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C9" s="1">
         <v>500</v>
@@ -1056,7 +1050,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C10" s="1">
         <v>385</v>
@@ -1091,7 +1085,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C11" s="1">
         <v>69</v>
@@ -1126,7 +1120,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C12" s="1">
         <v>74.5</v>
@@ -1161,7 +1155,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C13" s="1">
         <v>90</v>
@@ -1196,7 +1190,7 @@
         <v>17</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C14" s="1">
         <v>358</v>
@@ -1231,7 +1225,7 @@
         <v>16</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C15" s="1">
         <v>505</v>
@@ -1266,7 +1260,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C16" s="1">
         <v>694</v>
@@ -1301,7 +1295,7 @@
         <v>19</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C17" s="1">
         <v>160</v>
@@ -1336,7 +1330,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C18" s="1">
         <v>60</v>
@@ -1368,10 +1362,10 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C19" s="1">
         <v>284</v>
@@ -1406,7 +1400,7 @@
         <v>12</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C20" s="1">
         <f>VALUE(LEFT(L20,3))</f>
@@ -1445,31 +1439,31 @@
         <v>426</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="S20" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.3">
@@ -1477,7 +1471,7 @@
         <v>22</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C21" s="1">
         <v>395</v>
@@ -1512,7 +1506,7 @@
         <v>18</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C22" s="1">
         <v>45</v>
@@ -1547,7 +1541,7 @@
         <v>73</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C23" s="1">
         <v>84</v>
@@ -1582,7 +1576,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C24" s="1">
         <f>VALUE(LEFT(L24,3))</f>
@@ -1621,39 +1615,39 @@
         <v>1105</v>
       </c>
       <c r="L24" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="N24" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="M24" s="1" t="s">
+      <c r="O24" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="N24" s="1" t="s">
+      <c r="P24" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="O24" s="1" t="s">
+      <c r="Q24" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="P24" s="1" t="s">
+      <c r="R24" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="Q24" s="1" t="s">
+      <c r="S24" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="R24" s="1" t="s">
+      <c r="T24" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="S24" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="T24" s="1" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C25" s="1">
         <f>VALUE(LEFT(L25,3))</f>
@@ -1692,31 +1686,31 @@
         <v>700</v>
       </c>
       <c r="L25" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="N25" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="M25" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>126</v>
-      </c>
       <c r="O25" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="S25" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.3">
@@ -1727,10 +1721,10 @@
         <v>70</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.3">
@@ -1863,274 +1857,280 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>75</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H36" s="4"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H38" s="4"/>
+        <v>69</v>
+      </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
+        <v>71</v>
+      </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>69</v>
+        <v>153</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>156</v>
+        <v>33</v>
+      </c>
+      <c r="B42" s="1">
+        <v>19</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>72</v>
+        <v>34</v>
+      </c>
+      <c r="B43" s="1">
+        <v>50</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B44" s="1">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B45" s="1">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B47" s="1">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
+      </c>
+      <c r="B49" s="1">
+        <v>142</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="B50" s="1">
+        <v>100</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>40</v>
+        <v>146</v>
       </c>
       <c r="B51" s="1">
-        <v>142</v>
+        <v>44</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B52" s="1">
-        <v>100</v>
+        <v>147</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B53" s="1">
-        <v>44</v>
+        <v>148</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>153</v>
+        <v>42</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>154</v>
+        <v>43</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>76</v>
+        <v>44</v>
+      </c>
+      <c r="B59" s="1">
+        <v>27.2</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B61" s="1">
         <v>44</v>
-      </c>
-      <c r="B61" s="1">
-        <v>27.2</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B63" s="1">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="B64" s="1">
+        <v>180</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B66" s="1">
-        <v>180</v>
+        <v>51</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>137</v>
+        <v>53</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>136</v>
+        <v>54</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
+      </c>
+      <c r="B70" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
+      </c>
+      <c r="B71" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B72" s="1">
-        <v>2</v>
+        <v>57</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B73" s="1">
-        <v>1</v>
+        <v>58</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>72</v>
@@ -2138,7 +2138,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>72</v>
@@ -2146,7 +2146,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>72</v>
@@ -2154,55 +2154,39 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>72</v>
+        <v>62</v>
+      </c>
+      <c r="B77" s="1">
+        <v>1799</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>72</v>
+        <v>63</v>
+      </c>
+      <c r="B78" s="1">
+        <v>3599</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B79" s="1">
-        <v>1799</v>
+        <v>64</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B80" s="1">
-        <v>3599</v>
+        <v>65</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A82" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A83" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>
